--- a/tools/importer/reports/import-toplevel.report.xlsx
+++ b/tools/importer/reports/import-toplevel.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
   <si>
     <t>_reportFile</t>
   </si>
@@ -73,7 +73,7 @@
     <t>toplevel</t>
   </si>
   <si>
-    <t>2026-09-09T03:03:34.005Z</t>
+    <t>2026-09-09T05:34:13.830Z</t>
   </si>
   <si>
     <t>Explore</t>
@@ -85,13 +85,13 @@
     <t>en-us/learn.report.json</t>
   </si>
   <si>
-    <t>["hero-home","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","carousel-promo","carousel-promo","carousel-promo","carousel-promo","carousel-promo","video","video"]</t>
+    <t>["hero-home","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","carousel-promo","carousel-promo","carousel-promo","carousel-promo","carousel-promo","video","video","course-teaser"]</t>
   </si>
   <si>
     <t>en-us/learn</t>
   </si>
   <si>
-    <t>2026-09-09T03:03:50.501Z</t>
+    <t>2026-09-09T05:34:28.704Z</t>
   </si>
   <si>
     <t>DS Academy: Flexible Dental Education for Professional Growth</t>
@@ -100,6 +100,27 @@
     <t>https://www.dentsplysirona.com/en-us/learn.html</t>
   </si>
   <si>
+    <t>en-us/shop.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","cards-promo","cards-promo","cards-promo","cards-category","cards-category","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature"]</t>
+  </si>
+  <si>
+    <t>en-us/shop</t>
+  </si>
+  <si>
+    <t>shop</t>
+  </si>
+  <si>
+    <t>2026-09-09T03:29:04.102Z</t>
+  </si>
+  <si>
+    <t>Shop dental products and supplies here</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/shop.html</t>
+  </si>
+  <si>
     <t>en-us/support.report.json</t>
   </si>
   <si>
@@ -109,7 +130,7 @@
     <t>en-us/support</t>
   </si>
   <si>
-    <t>2026-09-09T03:04:21.149Z</t>
+    <t>2026-09-09T05:34:58.218Z</t>
   </si>
   <si>
     <t>Customer Support: FAQ's</t>
@@ -121,13 +142,13 @@
     <t>en-us/why-ds.report.json</t>
   </si>
   <si>
-    <t>["hero-home","cards-overlay","cards-overlay","cards-overlay","cards-overlay","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","carousel-promo","carousel-promo"]</t>
+    <t>["hero-home","cards-overlay","cards-overlay","cards-overlay","cards-overlay","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","carousel-promo","carousel-promo","course-teaser"]</t>
   </si>
   <si>
     <t>en-us/why-ds</t>
   </si>
   <si>
-    <t>2026-09-09T03:04:06.125Z</t>
+    <t>2026-09-09T05:34:42.901Z</t>
   </si>
   <si>
     <t>Why DS</t>
@@ -522,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -651,27 +672,27 @@
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
@@ -680,13 +701,39 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-toplevel.report.xlsx
+++ b/tools/importer/reports/import-toplevel.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-08T21:49:09.906Z</t>
+    <t>2026-09-09T06:27:35.607Z</t>
   </si>
   <si>
     <t>Dentsply Sirona USA: Dental products and technologies</t>
@@ -73,7 +73,7 @@
     <t>toplevel</t>
   </si>
   <si>
-    <t>2026-09-09T05:34:13.830Z</t>
+    <t>2026-09-09T06:27:59.044Z</t>
   </si>
   <si>
     <t>Explore</t>
@@ -91,7 +91,7 @@
     <t>en-us/learn</t>
   </si>
   <si>
-    <t>2026-09-09T05:34:28.704Z</t>
+    <t>2026-09-09T06:28:14.613Z</t>
   </si>
   <si>
     <t>DS Academy: Flexible Dental Education for Professional Growth</t>
@@ -112,7 +112,7 @@
     <t>shop</t>
   </si>
   <si>
-    <t>2026-09-09T03:29:04.102Z</t>
+    <t>2026-09-09T06:00:52.202Z</t>
   </si>
   <si>
     <t>Shop dental products and supplies here</t>
@@ -130,7 +130,7 @@
     <t>en-us/support</t>
   </si>
   <si>
-    <t>2026-09-09T05:34:58.218Z</t>
+    <t>2026-09-09T06:28:44.655Z</t>
   </si>
   <si>
     <t>Customer Support: FAQ's</t>
@@ -148,7 +148,7 @@
     <t>en-us/why-ds</t>
   </si>
   <si>
-    <t>2026-09-09T05:34:42.901Z</t>
+    <t>2026-09-09T06:28:29.308Z</t>
   </si>
   <si>
     <t>Why DS</t>

--- a/tools/importer/reports/import-toplevel.report.xlsx
+++ b/tools/importer/reports/import-toplevel.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="169">
   <si>
     <t>_reportFile</t>
   </si>
@@ -73,7 +73,7 @@
     <t>toplevel</t>
   </si>
   <si>
-    <t>2026-09-09T06:27:59.044Z</t>
+    <t>2026-09-09T07:26:25.103Z</t>
   </si>
   <si>
     <t>Explore</t>
@@ -91,7 +91,7 @@
     <t>en-us/learn</t>
   </si>
   <si>
-    <t>2026-09-09T06:28:14.613Z</t>
+    <t>2026-09-09T07:26:41.631Z</t>
   </si>
   <si>
     <t>DS Academy: Flexible Dental Education for Professional Growth</t>
@@ -112,7 +112,7 @@
     <t>shop</t>
   </si>
   <si>
-    <t>2026-09-09T06:00:52.202Z</t>
+    <t>2026-09-09T06:28:58.941Z</t>
   </si>
   <si>
     <t>Shop dental products and supplies here</t>
@@ -130,7 +130,7 @@
     <t>en-us/support</t>
   </si>
   <si>
-    <t>2026-09-09T06:28:44.655Z</t>
+    <t>2026-09-09T07:27:11.856Z</t>
   </si>
   <si>
     <t>Customer Support: FAQ's</t>
@@ -148,13 +148,376 @@
     <t>en-us/why-ds</t>
   </si>
   <si>
-    <t>2026-09-09T06:28:29.308Z</t>
+    <t>2026-09-09T07:26:57.809Z</t>
   </si>
   <si>
     <t>Why DS</t>
   </si>
   <si>
     <t>https://www.dentsplysirona.com/en-us/why-ds.html</t>
+  </si>
+  <si>
+    <t>en-us/explore/digital-dentistry.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","cards-overlay","cards-overlay","cards-overlay","cards-overlay","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","carousel-promo","carousel-promo","carousel-promo","accordion","accordion","accordion","accordion","course-teaser"]</t>
+  </si>
+  <si>
+    <t>en-us/explore/digital-dentistry</t>
+  </si>
+  <si>
+    <t>catalog</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:11:26.803Z</t>
+  </si>
+  <si>
+    <t>Explore Digital Dentistry with Dentsply Sirona</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/explore/digital-dentistry.html</t>
+  </si>
+  <si>
+    <t>en-us/explore/endodontics.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","cards-overlay","cards-overlay","cards-overlay","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","carousel-promo"]</t>
+  </si>
+  <si>
+    <t>en-us/explore/endodontics</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:12:31.603Z</t>
+  </si>
+  <si>
+    <t>Comprehensive Endodontic Solutions</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/explore/endodontics.html</t>
+  </si>
+  <si>
+    <t>en-us/explore/implant-dentistry.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home"]</t>
+  </si>
+  <si>
+    <t>en-us/explore/implant-dentistry</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:11:57.712Z</t>
+  </si>
+  <si>
+    <t>Dental Implant Systems: Discover now!</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/explore/implant-dentistry.html</t>
+  </si>
+  <si>
+    <t>en-us/explore/orthodontics.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","carousel-promo","carousel-promo","carousel-promo","carousel-promo"]</t>
+  </si>
+  <si>
+    <t>en-us/explore/orthodontics</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:12:15.079Z</t>
+  </si>
+  <si>
+    <t>Orthodontic Products &amp; Solutions</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/explore/orthodontics.html</t>
+  </si>
+  <si>
+    <t>en-us/explore/preventive.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","cards-overlay","cards-overlay","cards-overlay","cards-overlay","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","carousel-promo","carousel-promo","carousel-promo","carousel-promo","accordion","accordion","course-teaser"]</t>
+  </si>
+  <si>
+    <t>en-us/explore/preventive</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:12:48.028Z</t>
+  </si>
+  <si>
+    <t>Comprehensive preventive care solutions for healthier smiles</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/explore/preventive.html</t>
+  </si>
+  <si>
+    <t>en-us/explore/restorative.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","cards-overlay","cards-overlay","cards-overlay","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","carousel-promo","carousel-promo","carousel-promo","accordion","accordion"]</t>
+  </si>
+  <si>
+    <t>en-us/explore/restorative</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:11:41.504Z</t>
+  </si>
+  <si>
+    <t>Dental Restorative Products and more!</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/explore/restorative.html</t>
+  </si>
+  <si>
+    <t>en-us/support/help-topics.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","cards-overlay","cards-overlay","cards-overlay","cards-overlay","cards-overlay","cards-overlay","cards-overlay","cards-feature","cards-feature","cards-feature","cards-feature"]</t>
+  </si>
+  <si>
+    <t>en-us/support/help-topics</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:15:32.117Z</t>
+  </si>
+  <si>
+    <t>Help Topics</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/support/help-topics.html</t>
+  </si>
+  <si>
+    <t>en-us/learn/education/continuing-education.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","carousel-promo","carousel-promo","carousel-promo","carousel-promo","carousel-promo","accordion"]</t>
+  </si>
+  <si>
+    <t>en-us/learn/education/continuing-education</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:14:46.659Z</t>
+  </si>
+  <si>
+    <t>Dental Continuing Education with Courses &amp; Videos</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/learn/education/continuing-education.html</t>
+  </si>
+  <si>
+    <t>en-us/learn/education/practice-management-marketing.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","cards-feature","cards-feature","carousel-promo","carousel-promo","carousel-promo","carousel-promo"]</t>
+  </si>
+  <si>
+    <t>en-us/learn/education/practice-management-marketing</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:15:03.161Z</t>
+  </si>
+  <si>
+    <t>Practice Management &amp; Marketing Course-Overview</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/learn/education/practice-management---marketing.html</t>
+  </si>
+  <si>
+    <t>en-us/support/resources/download-center.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","cards-feature","carousel-promo"]</t>
+  </si>
+  <si>
+    <t>en-us/support/resources/download-center</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:15:48.977Z</t>
+  </si>
+  <si>
+    <t>IFU, SDS, Instructions for Use &amp; Safety Data Sheets USA</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/support/resources/download-center.html</t>
+  </si>
+  <si>
+    <t>en-us/why-ds/our-programs/one-ds.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","accordion","accordion","course-teaser"]</t>
+  </si>
+  <si>
+    <t>en-us/why-ds/our-programs/one-ds</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:15:17.827Z</t>
+  </si>
+  <si>
+    <t>ONE DS Loyalty Program: Rewards for Dental Professionals</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/why-ds/our-programs/one-ds.html</t>
+  </si>
+  <si>
+    <t>en-us/explore/digital-dentistry/brands/ds-core.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","cards-overlay","cards-overlay","cards-overlay","cards-overlay","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","carousel-promo","cards-quote","accordion","accordion","accordion","accordion","accordion","accordion","course-teaser"]</t>
+  </si>
+  <si>
+    <t>en-us/explore/digital-dentistry/brands/ds-core</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:13:06.897Z</t>
+  </si>
+  <si>
+    <t>Cloud Solution for Dentists: Clinical applications for streamlined dental workflows</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/explore/digital-dentistry/brands/ds-core.html</t>
+  </si>
+  <si>
+    <t>en-us/explore/digital-dentistry/brands/primescan-2.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-quote","accordion"]</t>
+  </si>
+  <si>
+    <t>en-us/explore/digital-dentistry/brands/primescan-2</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:13:24.604Z</t>
+  </si>
+  <si>
+    <t>Primescan 2</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/explore/digital-dentistry/brands/primescan-2.html</t>
+  </si>
+  <si>
+    <t>en-us/explore/digital-dentistry/product-topics/digital-impression.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","carousel-promo","carousel-promo","carousel-promo"]</t>
+  </si>
+  <si>
+    <t>en-us/explore/digital-dentistry/product-topics/digital-impression</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:16:40.705Z</t>
+  </si>
+  <si>
+    <t>Intraoral Dental Scanners</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/explore/digital-dentistry/product-topics/digital-impression.html</t>
+  </si>
+  <si>
+    <t>en-us/explore/endodontics/brands/waveone-gold.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","cards-overlay","cards-overlay","cards-overlay","cards-overlay","cards-overlay","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","carousel-promo","accordion","accordion","accordion","accordion"]</t>
+  </si>
+  <si>
+    <t>en-us/explore/endodontics/brands/waveone-gold</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:13:40.015Z</t>
+  </si>
+  <si>
+    <t>WaveOne Gold: Simplified root canal shaping &amp; obturation</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/explore/endodontics/brands/waveone-gold.html</t>
+  </si>
+  <si>
+    <t>en-us/explore/implant-dentistry/brands/astra-tech-implant-system-ev.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","cards-feature","cards-feature","cards-feature","cards-quote"]</t>
+  </si>
+  <si>
+    <t>en-us/explore/implant-dentistry/brands/astra-tech-implant-system-ev</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:13:58.098Z</t>
+  </si>
+  <si>
+    <t>Astra Tech Implant System EV</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/explore/implant-dentistry/brands/astra-tech-implant-system-ev.html</t>
+  </si>
+  <si>
+    <t>en-us/explore/implant-dentistry/product-topics/product-selection-guide.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","cards-feature","cards-feature","cards-feature","cards-feature","carousel-promo","course-teaser"]</t>
+  </si>
+  <si>
+    <t>en-us/explore/implant-dentistry/product-topics/product-selection-guide</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:16:24.115Z</t>
+  </si>
+  <si>
+    <t>Product Selection Guide USA</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/explore/implant-dentistry/product-topics/product-selection-guide.html</t>
+  </si>
+  <si>
+    <t>en-us/explore/orthodontics/brands/suresmile-clear-aligner.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","cards-quote","cards-quote"]</t>
+  </si>
+  <si>
+    <t>en-us/explore/orthodontics/brands/suresmile-clear-aligner</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:14:14.353Z</t>
+  </si>
+  <si>
+    <t>SureSmile Clear Aligner</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/explore/orthodontics/brands/suresmile-clear-aligner.html</t>
+  </si>
+  <si>
+    <t>en-us/explore/preventive/brands/cavitron-300.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","cards-overlay","cards-overlay","cards-overlay","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","carousel-promo","accordion","accordion","accordion","accordion","accordion","accordion","course-teaser"]</t>
+  </si>
+  <si>
+    <t>en-us/explore/preventive/brands/cavitron-300</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:14:30.639Z</t>
+  </si>
+  <si>
+    <t>Cavitron® 300 Series</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/explore/preventive/brands/cavitron-300.html</t>
+  </si>
+  <si>
+    <t>en-us/explore/restorative/brands/tph-spectra.report.json</t>
+  </si>
+  <si>
+    <t>["hero-home","cards-feature","cards-feature","cards-feature"]</t>
+  </si>
+  <si>
+    <t>en-us/explore/restorative/brands/tph-spectra</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:16:09.228Z</t>
+  </si>
+  <si>
+    <t>TPH Spectra® ST Family</t>
+  </si>
+  <si>
+    <t>https://www.dentsplysirona.com/en-us/explore/restorative/brands/tph-spectra-.html</t>
   </si>
 </sst>
 </file>
@@ -543,12 +906,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="8" width="50" customWidth="1"/>
@@ -736,6 +1097,526 @@
         <v>47</v>
       </c>
     </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" t="s">
+        <v>107</v>
+      </c>
+      <c r="H17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" t="s">
+        <v>112</v>
+      </c>
+      <c r="G18" t="s">
+        <v>113</v>
+      </c>
+      <c r="H18" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" t="s">
+        <v>119</v>
+      </c>
+      <c r="H19" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>121</v>
+      </c>
+      <c r="B20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G20" t="s">
+        <v>125</v>
+      </c>
+      <c r="H20" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" t="s">
+        <v>131</v>
+      </c>
+      <c r="H21" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" t="s">
+        <v>135</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" t="s">
+        <v>136</v>
+      </c>
+      <c r="G22" t="s">
+        <v>137</v>
+      </c>
+      <c r="H22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>139</v>
+      </c>
+      <c r="B23" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" t="s">
+        <v>141</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" t="s">
+        <v>142</v>
+      </c>
+      <c r="G23" t="s">
+        <v>143</v>
+      </c>
+      <c r="H23" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" t="s">
+        <v>148</v>
+      </c>
+      <c r="G24" t="s">
+        <v>149</v>
+      </c>
+      <c r="H24" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" t="s">
+        <v>152</v>
+      </c>
+      <c r="C25" t="s">
+        <v>153</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25" t="s">
+        <v>154</v>
+      </c>
+      <c r="G25" t="s">
+        <v>155</v>
+      </c>
+      <c r="H25" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>157</v>
+      </c>
+      <c r="B26" t="s">
+        <v>158</v>
+      </c>
+      <c r="C26" t="s">
+        <v>159</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" t="s">
+        <v>160</v>
+      </c>
+      <c r="G26" t="s">
+        <v>161</v>
+      </c>
+      <c r="H26" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>163</v>
+      </c>
+      <c r="B27" t="s">
+        <v>164</v>
+      </c>
+      <c r="C27" t="s">
+        <v>165</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" t="s">
+        <v>166</v>
+      </c>
+      <c r="G27" t="s">
+        <v>167</v>
+      </c>
+      <c r="H27" t="s">
+        <v>168</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
